--- a/outputs/july.xlsx
+++ b/outputs/july.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Week3" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Week4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Week5" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2894,4 +2895,626 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>30263.35</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>575.85</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>29758.5</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>30290</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>29758.5</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>12210</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>661.73</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>-13.76</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>675.51</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>680.05</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>661.14</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>55291184</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>07/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>63500.08</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>-415.09</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>63954.97</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>64733.89</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>63392.39</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>374</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>07/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>100.83</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>101.43</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>100.76</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.85781</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>0.00096</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.85685</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.85855</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.85619</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>479537</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>07/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.5658</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>-0.0056</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.5718</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.5655</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>731488</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>07/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.4048</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>-0.00602</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.4108</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1.41098</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.4024</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>327249</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>07/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.97701</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>-0.00684</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.98385</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.98453</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>330459</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>07/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>57.625</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>57.115</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>59.236</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>56.787</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>170634</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>07/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>4066.16</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>37.49</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4028.66</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>4115.87</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>3996.38</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>198286</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>07/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.5792</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.5808</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.5823</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>247255</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>07/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1.61099</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>0.00467</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1.60632</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1.61127</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1.60309</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>376379</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>07/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>163.416</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>-0.454</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>163.87</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>163.904</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>163.24</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>391675</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>07/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.93304</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>9.000000000000001e-05</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.93294</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.9345</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.93157</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>408298</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>07/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.8135599999999999</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>-0.00579</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.81935</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.82069</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.81332</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>361685</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>07/29/26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/july.xlsx
+++ b/outputs/july.xlsx
@@ -3076,9 +3076,7 @@
       <c r="G5" s="1" t="n">
         <v>100.76</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>
